--- a/Team-Data/2014-15/1-12-2014-15.xlsx
+++ b/Team-Data/2014-15/1-12-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>5.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -766,7 +833,7 @@
         <v>7</v>
       </c>
       <c r="AM2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN2" t="n">
         <v>3</v>
@@ -784,7 +851,7 @@
         <v>29</v>
       </c>
       <c r="AS2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
@@ -799,10 +866,10 @@
         <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ2" t="n">
         <v>2</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -843,28 +910,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
         <v>23</v>
       </c>
       <c r="G3" t="n">
-        <v>0.361</v>
+        <v>0.343</v>
       </c>
       <c r="H3" t="n">
         <v>48.7</v>
       </c>
       <c r="I3" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="J3" t="n">
         <v>88.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L3" t="n">
         <v>7.4</v>
@@ -876,19 +943,19 @@
         <v>0.322</v>
       </c>
       <c r="O3" t="n">
-        <v>15.1</v>
+        <v>14.8</v>
       </c>
       <c r="P3" t="n">
-        <v>20.1</v>
+        <v>19.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.755</v>
+        <v>0.751</v>
       </c>
       <c r="R3" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S3" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T3" t="n">
         <v>43.4</v>
@@ -897,7 +964,7 @@
         <v>25.3</v>
       </c>
       <c r="V3" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W3" t="n">
         <v>8.300000000000001</v>
@@ -912,19 +979,19 @@
         <v>21.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>102.6</v>
+        <v>102.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.2</v>
+        <v>-1.5</v>
       </c>
       <c r="AD3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE3" t="n">
         <v>26</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>25</v>
       </c>
       <c r="AF3" t="n">
         <v>21</v>
@@ -942,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL3" t="n">
         <v>14</v>
@@ -951,7 +1018,7 @@
         <v>13</v>
       </c>
       <c r="AN3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO3" t="n">
         <v>28</v>
@@ -960,22 +1027,22 @@
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT3" t="n">
         <v>12</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>11</v>
       </c>
       <c r="AU3" t="n">
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW3" t="n">
         <v>9</v>
@@ -984,10 +1051,10 @@
         <v>25</v>
       </c>
       <c r="AY3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
         <v>29</v>
@@ -996,7 +1063,7 @@
         <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -1025,22 +1092,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E4" t="n">
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G4" t="n">
-        <v>0.421</v>
+        <v>0.432</v>
       </c>
       <c r="H4" t="n">
         <v>48.7</v>
       </c>
       <c r="I4" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J4" t="n">
         <v>81.2</v>
@@ -1055,28 +1122,28 @@
         <v>21.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.321</v>
+        <v>0.323</v>
       </c>
       <c r="O4" t="n">
         <v>16.5</v>
       </c>
       <c r="P4" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.75</v>
+        <v>0.747</v>
       </c>
       <c r="R4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="S4" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T4" t="n">
         <v>42.4</v>
       </c>
       <c r="U4" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V4" t="n">
         <v>14.7</v>
@@ -1088,7 +1155,7 @@
         <v>4.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z4" t="n">
         <v>20.1</v>
@@ -1097,28 +1164,28 @@
         <v>20.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.5</v>
+        <v>-2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
       </c>
       <c r="AF4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ4" t="n">
         <v>24</v>
@@ -1133,7 +1200,7 @@
         <v>16</v>
       </c>
       <c r="AN4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO4" t="n">
         <v>22</v>
@@ -1142,22 +1209,22 @@
         <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR4" t="n">
         <v>26</v>
       </c>
       <c r="AS4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU4" t="n">
         <v>19</v>
       </c>
-      <c r="AU4" t="n">
-        <v>20</v>
-      </c>
       <c r="AV4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AW4" t="n">
         <v>21</v>
@@ -1169,7 +1236,7 @@
         <v>12</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
         <v>21</v>
@@ -1178,7 +1245,7 @@
         <v>25</v>
       </c>
       <c r="BC4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1370,7 @@
         <v>23</v>
       </c>
       <c r="AJ5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK5" t="n">
         <v>27</v>
@@ -1336,7 +1403,7 @@
         <v>13</v>
       </c>
       <c r="AU5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1351,7 +1418,7 @@
         <v>17</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA5" t="n">
         <v>7</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -1389,67 +1456,67 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E6" t="n">
         <v>26</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>0.667</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
       </c>
       <c r="I6" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J6" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L6" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M6" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0.354</v>
+        <v>0.356</v>
       </c>
       <c r="O6" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="P6" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.778</v>
+        <v>0.78</v>
       </c>
       <c r="R6" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S6" t="n">
         <v>33.8</v>
       </c>
       <c r="T6" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="U6" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V6" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W6" t="n">
         <v>6.1</v>
       </c>
       <c r="X6" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Y6" t="n">
         <v>5.4</v>
@@ -1461,31 +1528,31 @@
         <v>22.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>102.1</v>
+        <v>101.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE6" t="n">
         <v>4</v>
       </c>
       <c r="AF6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AH6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI6" t="n">
         <v>21</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK6" t="n">
         <v>20</v>
@@ -1497,7 +1564,7 @@
         <v>17</v>
       </c>
       <c r="AN6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1530,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ6" t="n">
         <v>3</v>
@@ -1539,7 +1606,7 @@
         <v>2</v>
       </c>
       <c r="BB6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1716,13 @@
         <v>-0.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE7" t="n">
         <v>14</v>
       </c>
       <c r="AF7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG7" t="n">
         <v>14</v>
@@ -1664,7 +1731,7 @@
         <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AJ7" t="n">
         <v>22</v>
@@ -1673,25 +1740,25 @@
         <v>18</v>
       </c>
       <c r="AL7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM7" t="n">
         <v>11</v>
       </c>
       <c r="AN7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS7" t="n">
         <v>27</v>
@@ -1724,7 +1791,7 @@
         <v>17</v>
       </c>
       <c r="BC7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -1753,34 +1820,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8" t="n">
         <v>26</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>0.703</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
       </c>
       <c r="I8" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="J8" t="n">
-        <v>86.5</v>
+        <v>86.3</v>
       </c>
       <c r="K8" t="n">
         <v>0.475</v>
       </c>
       <c r="L8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="M8" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="N8" t="n">
         <v>0.361</v>
@@ -1789,28 +1856,28 @@
         <v>17.2</v>
       </c>
       <c r="P8" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.76</v>
+        <v>0.762</v>
       </c>
       <c r="R8" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S8" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="T8" t="n">
-        <v>42.4</v>
+        <v>42.2</v>
       </c>
       <c r="U8" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V8" t="n">
         <v>12.2</v>
       </c>
       <c r="W8" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X8" t="n">
         <v>5</v>
@@ -1825,31 +1892,31 @@
         <v>22.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>109.1</v>
+        <v>108.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="n">
         <v>4</v>
       </c>
       <c r="AF8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AG8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AH8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK8" t="n">
         <v>2</v>
@@ -1858,7 +1925,7 @@
         <v>6</v>
       </c>
       <c r="AM8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN8" t="n">
         <v>11</v>
@@ -1867,46 +1934,46 @@
         <v>16</v>
       </c>
       <c r="AP8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
         <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW8" t="n">
         <v>11</v>
       </c>
       <c r="AX8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY8" t="n">
         <v>2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB8" t="n">
         <v>2</v>
       </c>
       <c r="BC8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -2013,10 +2080,10 @@
         <v>-1.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
         <v>17</v>
@@ -2028,13 +2095,13 @@
         <v>14</v>
       </c>
       <c r="AI9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AK9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL9" t="n">
         <v>12</v>
@@ -2064,10 +2131,10 @@
         <v>4</v>
       </c>
       <c r="AU9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW9" t="n">
         <v>24</v>
@@ -2085,10 +2152,10 @@
         <v>10</v>
       </c>
       <c r="BB9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -2117,25 +2184,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
         <v>24</v>
       </c>
       <c r="G10" t="n">
-        <v>0.368</v>
+        <v>0.351</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J10" t="n">
-        <v>86.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K10" t="n">
         <v>0.426</v>
@@ -2144,58 +2211,58 @@
         <v>8.6</v>
       </c>
       <c r="M10" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="N10" t="n">
         <v>0.345</v>
       </c>
       <c r="O10" t="n">
-        <v>15.8</v>
+        <v>15.5</v>
       </c>
       <c r="P10" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="S10" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="T10" t="n">
         <v>45.7</v>
       </c>
       <c r="U10" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V10" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W10" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA10" t="n">
         <v>19.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>97.7</v>
+        <v>97.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,10 +2274,10 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AI10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ10" t="n">
         <v>7</v>
@@ -2222,13 +2289,13 @@
         <v>9</v>
       </c>
       <c r="AM10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP10" t="n">
         <v>17</v>
@@ -2255,10 +2322,10 @@
         <v>14</v>
       </c>
       <c r="AX10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ10" t="n">
         <v>10</v>
@@ -2270,7 +2337,7 @@
         <v>22</v>
       </c>
       <c r="BC10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -2496,40 +2563,40 @@
         <v>48.5</v>
       </c>
       <c r="I12" t="n">
-        <v>36.4</v>
+        <v>36.1</v>
       </c>
       <c r="J12" t="n">
-        <v>83.40000000000001</v>
+        <v>83</v>
       </c>
       <c r="K12" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L12" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="M12" t="n">
-        <v>34.1</v>
+        <v>33.8</v>
       </c>
       <c r="N12" t="n">
         <v>0.349</v>
       </c>
       <c r="O12" t="n">
-        <v>17.1</v>
+        <v>17.6</v>
       </c>
       <c r="P12" t="n">
-        <v>24.1</v>
+        <v>24.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.708</v>
+        <v>0.706</v>
       </c>
       <c r="R12" t="n">
         <v>12.4</v>
       </c>
       <c r="S12" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T12" t="n">
-        <v>43.7</v>
+        <v>43.9</v>
       </c>
       <c r="U12" t="n">
         <v>20.7</v>
@@ -2541,25 +2608,25 @@
         <v>9.699999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.7</v>
+        <v>23.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.5</v>
+        <v>20.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>101.6</v>
+        <v>101.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2571,16 +2638,16 @@
         <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ12" t="n">
         <v>16</v>
       </c>
       <c r="AK12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL12" t="n">
         <v>1</v>
@@ -2592,10 +2659,10 @@
         <v>17</v>
       </c>
       <c r="AO12" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AP12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
@@ -2604,10 +2671,10 @@
         <v>4</v>
       </c>
       <c r="AS12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU12" t="n">
         <v>23</v>
@@ -2619,19 +2686,19 @@
         <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -2759,13 +2826,13 @@
         <v>27</v>
       </c>
       <c r="AJ13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK13" t="n">
         <v>28</v>
       </c>
       <c r="AL13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM13" t="n">
         <v>19</v>
@@ -2780,7 +2847,7 @@
         <v>23</v>
       </c>
       <c r="AQ13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR13" t="n">
         <v>12</v>
@@ -2804,7 +2871,7 @@
         <v>16</v>
       </c>
       <c r="AY13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ13" t="n">
         <v>17</v>
@@ -2816,7 +2883,7 @@
         <v>26</v>
       </c>
       <c r="BC13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -2923,13 +2990,13 @@
         <v>6.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE14" t="n">
         <v>8</v>
       </c>
       <c r="AF14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG14" t="n">
         <v>10</v>
@@ -2938,7 +3005,7 @@
         <v>26</v>
       </c>
       <c r="AI14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ14" t="n">
         <v>21</v>
@@ -2950,7 +3017,7 @@
         <v>2</v>
       </c>
       <c r="AM14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN14" t="n">
         <v>2</v>
@@ -2962,22 +3029,22 @@
         <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS14" t="n">
         <v>15</v>
       </c>
       <c r="AT14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU14" t="n">
         <v>5</v>
       </c>
       <c r="AV14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW14" t="n">
         <v>13</v>
@@ -2998,7 +3065,7 @@
         <v>5</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E15" t="n">
         <v>12</v>
       </c>
       <c r="F15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>0.324</v>
+        <v>0.316</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="J15" t="n">
-        <v>86.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.44</v>
+        <v>0.438</v>
       </c>
       <c r="L15" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M15" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="O15" t="n">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
       <c r="P15" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.745</v>
+        <v>0.747</v>
       </c>
       <c r="R15" t="n">
         <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="T15" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="U15" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V15" t="n">
         <v>12.5</v>
@@ -3090,94 +3157,94 @@
         <v>4.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>101.7</v>
+        <v>101.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.8</v>
+        <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AI15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AM15" t="n">
         <v>22</v>
       </c>
       <c r="AN15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR15" t="n">
         <v>9</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AS15" t="n">
         <v>20</v>
       </c>
-      <c r="AR15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>19</v>
-      </c>
       <c r="AT15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV15" t="n">
         <v>4</v>
       </c>
       <c r="AW15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY15" t="n">
         <v>7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3350,16 +3417,16 @@
         <v>22</v>
       </c>
       <c r="AY16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ16" t="n">
         <v>9</v>
       </c>
       <c r="BA16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC16" t="n">
         <v>9</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-4</v>
       </c>
       <c r="AD17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
         <v>18</v>
@@ -3490,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL17" t="n">
         <v>15</v>
@@ -3505,7 +3572,7 @@
         <v>9</v>
       </c>
       <c r="AP17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
         <v>26</v>
@@ -3538,10 +3605,10 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC17" t="n">
         <v>25</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3724,7 @@
         <v>13</v>
       </c>
       <c r="AF18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG18" t="n">
         <v>13</v>
@@ -3681,7 +3748,7 @@
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO18" t="n">
         <v>24</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-10.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3854,7 +3921,7 @@
         <v>8</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -3902,7 +3969,7 @@
         <v>15</v>
       </c>
       <c r="BA19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB19" t="n">
         <v>21</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -3940,100 +4007,100 @@
         <v>36</v>
       </c>
       <c r="E20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>0.472</v>
+        <v>0.5</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>38.6</v>
+        <v>38.8</v>
       </c>
       <c r="J20" t="n">
-        <v>84.09999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M20" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0.346</v>
+        <v>0.342</v>
       </c>
       <c r="O20" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="P20" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.77</v>
+        <v>0.755</v>
       </c>
       <c r="R20" t="n">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="S20" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="T20" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="U20" t="n">
         <v>21.4</v>
       </c>
       <c r="V20" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="W20" t="n">
         <v>7.4</v>
       </c>
       <c r="X20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB20" t="n">
         <v>101.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
         <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ20" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AK20" t="n">
         <v>13</v>
@@ -4045,25 +4112,25 @@
         <v>23</v>
       </c>
       <c r="AN20" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>14</v>
       </c>
-      <c r="AP20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ20" t="n">
+      <c r="AR20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT20" t="n">
         <v>11</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>14</v>
       </c>
       <c r="AU20" t="n">
         <v>14</v>
@@ -4075,13 +4142,13 @@
         <v>17</v>
       </c>
       <c r="AX20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
         <v>27</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA20" t="n">
         <v>26</v>
@@ -4090,7 +4157,7 @@
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4306,7 @@
         <v>7</v>
       </c>
       <c r="AR21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS21" t="n">
         <v>28</v>
@@ -4248,7 +4315,7 @@
         <v>29</v>
       </c>
       <c r="AU21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV21" t="n">
         <v>21</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -4379,16 +4446,16 @@
         <v>0.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE22" t="n">
         <v>15</v>
       </c>
       <c r="AF22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH22" t="n">
         <v>14</v>
@@ -4397,10 +4464,10 @@
         <v>17</v>
       </c>
       <c r="AJ22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL22" t="n">
         <v>17</v>
@@ -4439,16 +4506,16 @@
         <v>23</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
         <v>14</v>
       </c>
       <c r="AZ22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB22" t="n">
         <v>19</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -4486,79 +4553,79 @@
         <v>40</v>
       </c>
       <c r="E23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G23" t="n">
-        <v>0.35</v>
+        <v>0.325</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>36.9</v>
+        <v>36.5</v>
       </c>
       <c r="J23" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.45</v>
       </c>
       <c r="L23" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="N23" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O23" t="n">
         <v>13.7</v>
       </c>
       <c r="P23" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.723</v>
+        <v>0.728</v>
       </c>
       <c r="R23" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="S23" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="T23" t="n">
-        <v>40.4</v>
+        <v>41</v>
       </c>
       <c r="U23" t="n">
-        <v>20.2</v>
+        <v>19.9</v>
       </c>
       <c r="V23" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W23" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="Z23" t="n">
         <v>21.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.2</v>
+        <v>-5.8</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4570,19 +4637,19 @@
         <v>27</v>
       </c>
       <c r="AG23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH23" t="n">
         <v>28</v>
       </c>
       <c r="AI23" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AJ23" t="n">
         <v>26</v>
       </c>
       <c r="AK23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AL23" t="n">
         <v>21</v>
@@ -4603,28 +4670,28 @@
         <v>27</v>
       </c>
       <c r="AR23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU23" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AV23" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AW23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX23" t="n">
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
         <v>19</v>
@@ -4633,7 +4700,7 @@
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-12.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4767,7 +4834,7 @@
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM24" t="n">
         <v>10</v>
@@ -4779,22 +4846,22 @@
         <v>20</v>
       </c>
       <c r="AP24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT24" t="n">
         <v>21</v>
       </c>
       <c r="AU24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4803,10 +4870,10 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ24" t="n">
         <v>23</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4995,7 @@
         <v>1</v>
       </c>
       <c r="AE25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF25" t="n">
         <v>12</v>
@@ -4955,7 +5022,7 @@
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO25" t="n">
         <v>15</v>
@@ -4967,10 +5034,10 @@
         <v>1</v>
       </c>
       <c r="AR25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS25" t="n">
         <v>18</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>17</v>
       </c>
       <c r="AT25" t="n">
         <v>16</v>
@@ -4985,7 +5052,7 @@
         <v>7</v>
       </c>
       <c r="AX25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
         <v>6</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>7.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -5119,7 +5186,7 @@
         <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
         <v>6</v>
@@ -5128,7 +5195,7 @@
         <v>2</v>
       </c>
       <c r="AK26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
         <v>3</v>
@@ -5173,7 +5240,7 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA26" t="n">
         <v>25</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-1.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE27" t="n">
         <v>18</v>
@@ -5304,7 +5371,7 @@
         <v>6</v>
       </c>
       <c r="AI27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ27" t="n">
         <v>28</v>
@@ -5319,7 +5386,7 @@
         <v>29</v>
       </c>
       <c r="AN27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F28" t="n">
         <v>15</v>
       </c>
       <c r="G28" t="n">
-        <v>0.595</v>
+        <v>0.605</v>
       </c>
       <c r="H28" t="n">
         <v>49.2</v>
@@ -5411,43 +5478,43 @@
         <v>38.5</v>
       </c>
       <c r="J28" t="n">
-        <v>82.8</v>
+        <v>82.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.465</v>
+        <v>0.467</v>
       </c>
       <c r="L28" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.371</v>
+        <v>0.375</v>
       </c>
       <c r="O28" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P28" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="R28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="T28" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U28" t="n">
         <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W28" t="n">
         <v>7.5</v>
@@ -5456,10 +5523,10 @@
         <v>5.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA28" t="n">
         <v>20.5</v>
@@ -5471,7 +5538,7 @@
         <v>3.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>11</v>
@@ -5483,19 +5550,19 @@
         <v>11</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI28" t="n">
         <v>11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
         <v>6</v>
       </c>
       <c r="AL28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
         <v>15</v>
@@ -5510,7 +5577,7 @@
         <v>20</v>
       </c>
       <c r="AQ28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR28" t="n">
         <v>25</v>
@@ -5519,13 +5586,13 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW28" t="n">
         <v>16</v>
@@ -5540,10 +5607,10 @@
         <v>8</v>
       </c>
       <c r="BA28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -5575,94 +5642,94 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E29" t="n">
         <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>0.676</v>
+        <v>0.694</v>
       </c>
       <c r="H29" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I29" t="n">
-        <v>39.4</v>
+        <v>39.2</v>
       </c>
       <c r="J29" t="n">
-        <v>85.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="K29" t="n">
-        <v>0.462</v>
+        <v>0.46</v>
       </c>
       <c r="L29" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M29" t="n">
         <v>25.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.361</v>
+        <v>0.364</v>
       </c>
       <c r="O29" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="P29" t="n">
-        <v>25.3</v>
+        <v>25.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="R29" t="n">
         <v>11.3</v>
       </c>
       <c r="S29" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T29" t="n">
         <v>41.8</v>
       </c>
       <c r="U29" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="V29" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="W29" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y29" t="n">
         <v>5.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>107.8</v>
+        <v>107.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AE29" t="n">
         <v>8</v>
       </c>
       <c r="AF29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH29" t="n">
         <v>10</v>
@@ -5674,7 +5741,7 @@
         <v>9</v>
       </c>
       <c r="AK29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL29" t="n">
         <v>8</v>
@@ -5683,7 +5750,7 @@
         <v>7</v>
       </c>
       <c r="AN29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO29" t="n">
         <v>3</v>
@@ -5704,25 +5771,25 @@
         <v>22</v>
       </c>
       <c r="AU29" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AV29" t="n">
         <v>2</v>
       </c>
       <c r="AW29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY29" t="n">
         <v>20</v>
       </c>
-      <c r="AX29" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>19</v>
-      </c>
       <c r="AZ29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BB29" t="n">
         <v>3</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -5835,16 +5902,16 @@
         <v>-3.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF30" t="n">
         <v>25</v>
       </c>
       <c r="AG30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH30" t="n">
         <v>29</v>
@@ -5856,7 +5923,7 @@
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL30" t="n">
         <v>23</v>
@@ -5874,19 +5941,19 @@
         <v>13</v>
       </c>
       <c r="AQ30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
       </c>
       <c r="AT30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV30" t="n">
         <v>23</v>
@@ -5895,7 +5962,7 @@
         <v>25</v>
       </c>
       <c r="AX30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY30" t="n">
         <v>11</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>2</v>
       </c>
       <c r="AD31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE31" t="n">
         <v>8</v>
@@ -6026,7 +6093,7 @@
         <v>7</v>
       </c>
       <c r="AG31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH31" t="n">
         <v>14</v>
@@ -6050,7 +6117,7 @@
         <v>1</v>
       </c>
       <c r="AO31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP31" t="n">
         <v>25</v>
@@ -6071,7 +6138,7 @@
         <v>4</v>
       </c>
       <c r="AV31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AW31" t="n">
         <v>12</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-12-2014-15</t>
+          <t>2015-01-12</t>
         </is>
       </c>
     </row>
